--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123747240</v>
       </c>
       <c r="B2" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>123747245</v>
       </c>
       <c r="B3" t="n">
-        <v>58132</v>
+        <v>58135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123747240</v>
+        <v>123747245</v>
       </c>
       <c r="B2" t="n">
-        <v>57641</v>
+        <v>58136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123747245</v>
+        <v>123747240</v>
       </c>
       <c r="B3" t="n">
-        <v>58135</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +835,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -916,6 +916,126 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123929422</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57861</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lanetorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>414401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6249783</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123747245</v>
+        <v>123747240</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123747240</v>
+        <v>123747245</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>58136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,11 +839,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123747240</v>
+        <v>123747245</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
+        <v>58136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123747245</v>
+        <v>123747240</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +835,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123747240</v>
+        <v>123929422</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +710,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>414423</v>
+        <v>414401</v>
       </c>
       <c r="R2" t="n">
-        <v>6249726</v>
+        <v>6249783</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,22 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123747245</v>
+        <v>123747240</v>
       </c>
       <c r="B3" t="n">
-        <v>58158</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +825,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,32 +909,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929422</v>
+        <v>123747245</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>414401</v>
+        <v>414423</v>
       </c>
       <c r="R4" t="n">
-        <v>6249783</v>
+        <v>6249726</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,22 +982,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8253-2025 artfynd.xlsx
+++ b/artfynd/A 8253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123929422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123747240</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,8 +1036,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123747245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>